--- a/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,51</t>
+          <t>-2,03; 4,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,49</t>
+          <t>0,65; 7,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,83</t>
+          <t>-4,74; 2,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 9,38</t>
+          <t>-1,63; 9,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 81,75</t>
+          <t>-23,85; 84,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 201,98</t>
+          <t>5,25; 203,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 50,74</t>
+          <t>-48,66; 44,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 668,14</t>
+          <t>-49,3; 700,99</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,47</t>
+          <t>-1,26; 4,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,85</t>
+          <t>2,39; 8,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,76</t>
+          <t>-3,84; 1,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,35</t>
+          <t>-1,4; 2,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 93,18</t>
+          <t>-16,68; 100,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,59; 223,47</t>
+          <t>37,89; 239,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 37,26</t>
+          <t>-47,65; 34,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,04; 1871,5</t>
+          <t>-80,26; 1619,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,97</t>
+          <t>1,46; 7,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 6,18</t>
+          <t>-0,3; 6,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,01</t>
+          <t>-0,21; 4,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,01</t>
+          <t>-1,86; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,35; 234,76</t>
+          <t>27,58; 238,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 101,95</t>
+          <t>-3,5; 103,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 145,28</t>
+          <t>-4,34; 134,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 103,75</t>
+          <t>-31,7; 112,9</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,87</t>
+          <t>-1,58; 3,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,84</t>
+          <t>-2,95; 2,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,52</t>
+          <t>-2,02; 2,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,5</t>
+          <t>-1,24; 2,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 137,75</t>
+          <t>-31,5; 130,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 55,71</t>
+          <t>-52,25; 63,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 104,22</t>
+          <t>-40,39; 96,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 244,93</t>
+          <t>-38,27; 241,44</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,94</t>
+          <t>-2,57; 2,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,41</t>
+          <t>-2,19; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,99</t>
+          <t>-1,44; 3,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,61</t>
+          <t>-2,34; 0,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 112,17</t>
+          <t>-48,34; 118,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 141,78</t>
+          <t>-53,02; 136,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,35; 251,2</t>
+          <t>-47,11; 262,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 61,06</t>
+          <t>-76,12; 54,56</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,78</t>
+          <t>-3,84; 1,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -0,41</t>
+          <t>-5,01; -0,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,94</t>
+          <t>-1,59; 3,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,97; -0,22</t>
+          <t>-2,93; -0,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,64; 53,23</t>
+          <t>-77,95; 77,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,04</t>
+          <t>-94,11; -7,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 331,39</t>
+          <t>-59,66; 401,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-94,54; -19,2</t>
+          <t>-95,84; -18,59</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,31</t>
+          <t>-2,72; 2,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,31</t>
+          <t>-3,25; 1,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,95</t>
+          <t>-2,43; 2,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,26</t>
+          <t>-2,01; 0,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 296,45</t>
+          <t>-78,32; 291,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-88,9; 207,95</t>
+          <t>-88,51; 244,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 408,22</t>
+          <t>-89,26; 554,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,76</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,26</t>
+          <t>-0,08; 2,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,45</t>
+          <t>0,3; 2,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,22</t>
+          <t>-0,74; 1,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,06</t>
+          <t>-0,74; 1,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 52,72</t>
+          <t>-1,31; 51,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 57,46</t>
+          <t>5,6; 59,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 32,01</t>
+          <t>-15,54; 35,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 59,69</t>
+          <t>-25,67; 63,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>4,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>121,32%</t>
+          <t>141,82%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,97</t>
+          <t>-2,16; 4,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,64</t>
+          <t>1,0; 7,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 2,59</t>
+          <t>-4,88; 2,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 9,17</t>
+          <t>-0,23; 9,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 84,92</t>
+          <t>-24,62; 81,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 203,65</t>
+          <t>11,11; 210,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,66; 44,94</t>
+          <t>-49,35; 47,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 700,99</t>
+          <t>-25,46; 822,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>107,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,63</t>
+          <t>-1,35; 4,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,48</t>
+          <t>1,99; 7,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,73</t>
+          <t>-3,71; 1,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,29</t>
+          <t>-0,54; 3,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 100,57</t>
+          <t>-19,18; 93,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,89; 239,83</t>
+          <t>29,14; 222,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 34,89</t>
+          <t>-47,08; 40,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,26; 1619,57</t>
+          <t>-41,47; 643,44</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,01</t>
+          <t>1,67; 7,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 6,06</t>
+          <t>-0,27; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,87</t>
+          <t>-0,24; 4,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,23</t>
+          <t>-0,77; 4,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,58; 238,15</t>
+          <t>29,38; 240,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 103,31</t>
+          <t>-3,1; 94,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 134,43</t>
+          <t>-5,34; 144,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 112,9</t>
+          <t>-11,68; 119,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>-3,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,74</t>
+          <t>-1,46; 3,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,04</t>
+          <t>-2,77; 1,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,5</t>
+          <t>-2,01; 2,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,3</t>
+          <t>-1,91; 1,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 130,49</t>
+          <t>-29,19; 132,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,25; 63,48</t>
+          <t>-51,0; 57,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 96,42</t>
+          <t>-41,02; 92,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 241,44</t>
+          <t>-43,87; 78,74</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-36,03%</t>
+          <t>-38,57%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,99</t>
+          <t>-2,58; 3,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,37</t>
+          <t>-2,15; 2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,3</t>
+          <t>-1,2; 3,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,56</t>
+          <t>-2,61; 0,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,34; 118,44</t>
+          <t>-50,87; 115,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 136,31</t>
+          <t>-56,36; 132,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,11; 262,19</t>
+          <t>-41,72; 229,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-76,12; 54,56</t>
+          <t>-75,85; 32,5</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-73,95%</t>
+          <t>-52,3%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,03</t>
+          <t>-3,77; 1,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,01; -0,56</t>
+          <t>-5,09; -0,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,14</t>
+          <t>-1,56; 2,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,2</t>
+          <t>-2,49; 0,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,95; 77,66</t>
+          <t>-80,09; 80,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-94,11; -7,91</t>
+          <t>-94,92; 1,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 401,35</t>
+          <t>-62,86; 357,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,84; -18,59</t>
+          <t>-84,71; 39,31</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-63,2%</t>
+          <t>-57,21%</t>
         </is>
       </c>
     </row>
@@ -1260,37 +1260,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,28</t>
+          <t>-2,6; 2,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,26</t>
+          <t>-3,24; 1,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,18</t>
+          <t>-2,48; 1,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,26</t>
+          <t>-2,11; 0,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-78,32; 291,06</t>
+          <t>-80,13; 248,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-88,51; 244,1</t>
+          <t>-86,55; 276,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-89,26; 554,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,21</t>
+          <t>0,06; 2,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,51</t>
+          <t>0,21; 2,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,39</t>
+          <t>-0,78; 1,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,12</t>
+          <t>-0,29; 1,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 51,23</t>
+          <t>1,01; 52,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 59,0</t>
+          <t>3,55; 58,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 35,87</t>
+          <t>-16,12; 32,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 63,23</t>
+          <t>-9,19; 61,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
